--- a/Mechanical_Engineering_Allotment.xlsx
+++ b/Mechanical_Engineering_Allotment.xlsx
@@ -574,19 +574,19 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>Arjun Binu</v>
+        <v>Adharsh Reji</v>
       </c>
       <c r="C8" t="str">
-        <v>1044</v>
+        <v>1169</v>
       </c>
       <c r="D8" t="str">
         <v>SM</v>
       </c>
       <c r="E8" t="str">
-        <v>arjunbinucs00@gmail.com</v>
+        <v>adarshreji08@gmail.com</v>
       </c>
       <c r="F8" t="str">
-        <v>7902241606</v>
+        <v>8590699763</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -597,19 +597,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>Adharsh Reji</v>
+        <v>Akshay Subhash</v>
       </c>
       <c r="C9" t="str">
-        <v>1169</v>
+        <v>1665</v>
       </c>
       <c r="D9" t="str">
         <v>SM</v>
       </c>
       <c r="E9" t="str">
-        <v>adarshreji08@gmail.com</v>
+        <v>akshayabhi465@gmail.com</v>
       </c>
       <c r="F9" t="str">
-        <v>8590699763</v>
+        <v>7994904495</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -620,19 +620,19 @@
         <v>7</v>
       </c>
       <c r="B10" t="str">
-        <v>DEEPU V NAIR</v>
+        <v>ANANDAMOORTHY S</v>
       </c>
       <c r="C10" t="str">
-        <v>1545</v>
+        <v>2329</v>
       </c>
       <c r="D10" t="str">
         <v>SM</v>
       </c>
       <c r="E10" t="str">
-        <v>deepuvnair2002@gmail.com</v>
+        <v>anandamoorthy06@gmail.com</v>
       </c>
       <c r="F10" t="str">
-        <v>7356682559</v>
+        <v>7909295156</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -643,19 +643,19 @@
         <v>8</v>
       </c>
       <c r="B11" t="str">
-        <v>Akshay Subhash</v>
+        <v>Jishnu saseendran</v>
       </c>
       <c r="C11" t="str">
-        <v>1665</v>
+        <v>2415</v>
       </c>
       <c r="D11" t="str">
         <v>SM</v>
       </c>
       <c r="E11" t="str">
-        <v>akshayabhi465@gmail.com</v>
+        <v>jishnusaseendran82@gmail.com</v>
       </c>
       <c r="F11" t="str">
-        <v>7994904495</v>
+        <v>9633036381</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -666,19 +666,19 @@
         <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>Ramesh Kumar K G</v>
+        <v>VIBIN VASANTH</v>
       </c>
       <c r="C12" t="str">
-        <v>2241</v>
+        <v>3158</v>
       </c>
       <c r="D12" t="str">
         <v>SM</v>
       </c>
       <c r="E12" t="str">
-        <v>rameshveettoor@gmail.com</v>
+        <v>vibinvasanth2255@gmail.com</v>
       </c>
       <c r="F12" t="str">
-        <v>9447821426</v>
+        <v>8078071210</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -689,19 +689,19 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>ANANDAMOORTHY S</v>
+        <v>VIPIN S R</v>
       </c>
       <c r="C13" t="str">
-        <v>2329</v>
+        <v>4056</v>
       </c>
       <c r="D13" t="str">
         <v>SM</v>
       </c>
       <c r="E13" t="str">
-        <v>anandamoorthy06@gmail.com</v>
+        <v>vipinsroottara@gmail.com</v>
       </c>
       <c r="F13" t="str">
-        <v>7909295156</v>
+        <v>9447446331</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -712,19 +712,19 @@
         <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>Sethumadhavan Sk</v>
+        <v>Albin Raj R</v>
       </c>
       <c r="C14" t="str">
-        <v>2358</v>
+        <v>4382</v>
       </c>
       <c r="D14" t="str">
         <v>SM</v>
       </c>
       <c r="E14" t="str">
-        <v>sksethumadhavan@gmail.com</v>
+        <v>albinrajr52@gmail.com</v>
       </c>
       <c r="F14" t="str">
-        <v>9496935402</v>
+        <v>7994723176</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -735,19 +735,19 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>Vishnu.M</v>
+        <v>AMAL M</v>
       </c>
       <c r="C15" t="str">
-        <v>2419</v>
+        <v>4553</v>
       </c>
       <c r="D15" t="str">
         <v>SM</v>
       </c>
       <c r="E15" t="str">
-        <v>vishnumukundan2021@gmail.com</v>
+        <v>amalmahesh42@gmail.com</v>
       </c>
       <c r="F15" t="str">
-        <v>9400387476</v>
+        <v>7902318852</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -758,19 +758,19 @@
         <v>13</v>
       </c>
       <c r="B16" t="str">
-        <v>MUNEER M</v>
+        <v>MOHAN RAM</v>
       </c>
       <c r="C16" t="str">
-        <v>3006</v>
+        <v>180</v>
       </c>
       <c r="D16" t="str">
         <v>SM</v>
       </c>
       <c r="E16" t="str">
-        <v>muneer.m@myyahoo.com</v>
+        <v>mohanprajapati.2121@gmail.com</v>
       </c>
       <c r="F16" t="str">
-        <v>7356630023</v>
+        <v>8890350192</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>14</v>
       </c>
       <c r="B17" t="str">
-        <v>Adhithya Krishna S L</v>
+        <v>Sonu Kumar singh</v>
       </c>
       <c r="C17" t="str">
-        <v>3051</v>
+        <v>446</v>
       </c>
       <c r="D17" t="str">
         <v>SM</v>
       </c>
       <c r="E17" t="str">
-        <v>adhikrishna635@gmail.com</v>
+        <v>sk785045@gmail.com</v>
       </c>
       <c r="F17" t="str">
-        <v>9995334216</v>
+        <v>6203012639</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -804,19 +804,19 @@
         <v>15</v>
       </c>
       <c r="B18" t="str">
-        <v>ABHISHEK S</v>
+        <v>Arjun Binu</v>
       </c>
       <c r="C18" t="str">
-        <v>3064</v>
+        <v>1044</v>
       </c>
       <c r="D18" t="str">
         <v>SM</v>
       </c>
       <c r="E18" t="str">
-        <v>abhishekabhishek4363@gmail.com</v>
+        <v>arjunbinucs00@gmail.com</v>
       </c>
       <c r="F18" t="str">
-        <v>6282597658</v>
+        <v>7902241606</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -827,19 +827,19 @@
         <v>16</v>
       </c>
       <c r="B19" t="str">
-        <v>VIBIN VASANTH</v>
+        <v>Ramesh Kumar K G</v>
       </c>
       <c r="C19" t="str">
-        <v>3158</v>
+        <v>2241</v>
       </c>
       <c r="D19" t="str">
-        <v>EZ</v>
+        <v>BH</v>
       </c>
       <c r="E19" t="str">
-        <v>vibinvasanth2255@gmail.com</v>
+        <v>rameshveettoor@gmail.com</v>
       </c>
       <c r="F19" t="str">
-        <v>8078071210</v>
+        <v>9447821426</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -850,19 +850,19 @@
         <v>17</v>
       </c>
       <c r="B20" t="str">
-        <v>VIPIN S R</v>
+        <v>Vishnu.M</v>
       </c>
       <c r="C20" t="str">
-        <v>4056</v>
+        <v>2419</v>
       </c>
       <c r="D20" t="str">
-        <v>EZ</v>
+        <v>STAFF</v>
       </c>
       <c r="E20" t="str">
-        <v>vipinsroottara@gmail.com</v>
+        <v>vishnumukundan2021@gmail.com</v>
       </c>
       <c r="F20" t="str">
-        <v>9447446331</v>
+        <v>9400387476</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -873,19 +873,19 @@
         <v>18</v>
       </c>
       <c r="B21" t="str">
-        <v>Albin Raj R</v>
+        <v>ELDHO SHAMON</v>
       </c>
       <c r="C21" t="str">
-        <v>4382</v>
+        <v>3735</v>
       </c>
       <c r="D21" t="str">
-        <v>LC</v>
+        <v>SM-Vacant</v>
       </c>
       <c r="E21" t="str">
-        <v>albinrajr52@gmail.com</v>
+        <v>eldhoshamon888@gmail.com</v>
       </c>
       <c r="F21" t="str">
-        <v>7994723176</v>
+        <v>9544063925</v>
       </c>
       <c r="G21" t="str">
         <v/>
